--- a/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
+++ b/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Đúng 1</t>
   </si>
   <si>
-    <t>case2_valid1_1791232548812@company.local</t>
+    <t>case2_valid1_1791313638710@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
@@ -41,7 +41,7 @@
     <t>Nhân sự Đúng 2</t>
   </si>
   <si>
-    <t>case2_valid2_1791232548812@company.local</t>
+    <t>case2_valid2_1791313638710@company.local</t>
   </si>
   <si>
     <t>INTERVIEWER</t>
@@ -56,7 +56,7 @@
     <t>Nhân sự Đúng 3</t>
   </si>
   <si>
-    <t>case2_valid3_1791232548812@company.local</t>
+    <t>case2_valid3_1791313638710@company.local</t>
   </si>
   <si>
     <t>Nhân sự</t>
@@ -68,7 +68,7 @@
     <t>Nhân sự Đúng 4</t>
   </si>
   <si>
-    <t>case2_valid4_1791232548812@company.local</t>
+    <t>case2_valid4_1791313638710@company.local</t>
   </si>
   <si>
     <t>RECRUITER</t>
@@ -77,7 +77,7 @@
     <t/>
   </si>
   <si>
-    <t>case2_empty_name_1791232548812@company.local</t>
+    <t>case2_empty_name_1791313638710@company.local</t>
   </si>
   <si>
     <t>Tài chính</t>
@@ -86,13 +86,13 @@
     <t>Nhân sự Đúng 5</t>
   </si>
   <si>
-    <t>case2_valid5_1791232548812@company.local</t>
+    <t>case2_valid5_1791313638710@company.local</t>
   </si>
   <si>
     <t>Nhân sự Đúng 6</t>
   </si>
   <si>
-    <t>case2_valid6_1791232548812@company.local</t>
+    <t>case2_valid6_1791313638710@company.local</t>
   </si>
   <si>
     <t>Vận hành</t>
@@ -101,7 +101,7 @@
     <t>Nhân sự Lỗi 3 Role Sai</t>
   </si>
   <si>
-    <t>case2_invalid_role_1791232548812@company.local</t>
+    <t>case2_invalid_role_1791313638710@company.local</t>
   </si>
   <si>
     <t>INVALID_ROLE_XYZ</t>
@@ -110,7 +110,7 @@
     <t>Nhân sự Đúng 7</t>
   </si>
   <si>
-    <t>case2_valid7_1791232548812@company.local</t>
+    <t>case2_valid7_1791313638710@company.local</t>
   </si>
 </sst>
 </file>

--- a/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
+++ b/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Đúng 1</t>
   </si>
   <si>
-    <t>case2_valid1_1791313638710@company.local</t>
+    <t>case2_valid1_1791364218252@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
@@ -41,7 +41,7 @@
     <t>Nhân sự Đúng 2</t>
   </si>
   <si>
-    <t>case2_valid2_1791313638710@company.local</t>
+    <t>case2_valid2_1791364218252@company.local</t>
   </si>
   <si>
     <t>INTERVIEWER</t>
@@ -56,7 +56,7 @@
     <t>Nhân sự Đúng 3</t>
   </si>
   <si>
-    <t>case2_valid3_1791313638710@company.local</t>
+    <t>case2_valid3_1791364218252@company.local</t>
   </si>
   <si>
     <t>Nhân sự</t>
@@ -68,7 +68,7 @@
     <t>Nhân sự Đúng 4</t>
   </si>
   <si>
-    <t>case2_valid4_1791313638710@company.local</t>
+    <t>case2_valid4_1791364218252@company.local</t>
   </si>
   <si>
     <t>RECRUITER</t>
@@ -77,7 +77,7 @@
     <t/>
   </si>
   <si>
-    <t>case2_empty_name_1791313638710@company.local</t>
+    <t>case2_empty_name_1791364218252@company.local</t>
   </si>
   <si>
     <t>Tài chính</t>
@@ -86,13 +86,13 @@
     <t>Nhân sự Đúng 5</t>
   </si>
   <si>
-    <t>case2_valid5_1791313638710@company.local</t>
+    <t>case2_valid5_1791364218252@company.local</t>
   </si>
   <si>
     <t>Nhân sự Đúng 6</t>
   </si>
   <si>
-    <t>case2_valid6_1791313638710@company.local</t>
+    <t>case2_valid6_1791364218252@company.local</t>
   </si>
   <si>
     <t>Vận hành</t>
@@ -101,7 +101,7 @@
     <t>Nhân sự Lỗi 3 Role Sai</t>
   </si>
   <si>
-    <t>case2_invalid_role_1791313638710@company.local</t>
+    <t>case2_invalid_role_1791364218252@company.local</t>
   </si>
   <si>
     <t>INVALID_ROLE_XYZ</t>
@@ -110,7 +110,7 @@
     <t>Nhân sự Đúng 7</t>
   </si>
   <si>
-    <t>case2_valid7_1791313638710@company.local</t>
+    <t>case2_valid7_1791364218252@company.local</t>
   </si>
 </sst>
 </file>

--- a/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
+++ b/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Đúng 1</t>
   </si>
   <si>
-    <t>case2_valid1_1791364218252@company.local</t>
+    <t>case2_valid1_1791476314118@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
@@ -41,7 +41,7 @@
     <t>Nhân sự Đúng 2</t>
   </si>
   <si>
-    <t>case2_valid2_1791364218252@company.local</t>
+    <t>case2_valid2_1791476314118@company.local</t>
   </si>
   <si>
     <t>INTERVIEWER</t>
@@ -56,7 +56,7 @@
     <t>Nhân sự Đúng 3</t>
   </si>
   <si>
-    <t>case2_valid3_1791364218252@company.local</t>
+    <t>case2_valid3_1791476314118@company.local</t>
   </si>
   <si>
     <t>Nhân sự</t>
@@ -68,7 +68,7 @@
     <t>Nhân sự Đúng 4</t>
   </si>
   <si>
-    <t>case2_valid4_1791364218252@company.local</t>
+    <t>case2_valid4_1791476314118@company.local</t>
   </si>
   <si>
     <t>RECRUITER</t>
@@ -77,7 +77,7 @@
     <t/>
   </si>
   <si>
-    <t>case2_empty_name_1791364218252@company.local</t>
+    <t>case2_empty_name_1791476314118@company.local</t>
   </si>
   <si>
     <t>Tài chính</t>
@@ -86,13 +86,13 @@
     <t>Nhân sự Đúng 5</t>
   </si>
   <si>
-    <t>case2_valid5_1791364218252@company.local</t>
+    <t>case2_valid5_1791476314118@company.local</t>
   </si>
   <si>
     <t>Nhân sự Đúng 6</t>
   </si>
   <si>
-    <t>case2_valid6_1791364218252@company.local</t>
+    <t>case2_valid6_1791476314118@company.local</t>
   </si>
   <si>
     <t>Vận hành</t>
@@ -101,7 +101,7 @@
     <t>Nhân sự Lỗi 3 Role Sai</t>
   </si>
   <si>
-    <t>case2_invalid_role_1791364218252@company.local</t>
+    <t>case2_invalid_role_1791476314118@company.local</t>
   </si>
   <si>
     <t>INVALID_ROLE_XYZ</t>
@@ -110,7 +110,7 @@
     <t>Nhân sự Đúng 7</t>
   </si>
   <si>
-    <t>case2_valid7_1791364218252@company.local</t>
+    <t>case2_valid7_1791476314118@company.local</t>
   </si>
 </sst>
 </file>

--- a/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
+++ b/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Đúng 1</t>
   </si>
   <si>
-    <t>case2_valid1_1791476314118@company.local</t>
+    <t>case2_valid1_1791567428307@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
@@ -41,7 +41,7 @@
     <t>Nhân sự Đúng 2</t>
   </si>
   <si>
-    <t>case2_valid2_1791476314118@company.local</t>
+    <t>case2_valid2_1791567428307@company.local</t>
   </si>
   <si>
     <t>INTERVIEWER</t>
@@ -56,7 +56,7 @@
     <t>Nhân sự Đúng 3</t>
   </si>
   <si>
-    <t>case2_valid3_1791476314118@company.local</t>
+    <t>case2_valid3_1791567428307@company.local</t>
   </si>
   <si>
     <t>Nhân sự</t>
@@ -68,7 +68,7 @@
     <t>Nhân sự Đúng 4</t>
   </si>
   <si>
-    <t>case2_valid4_1791476314118@company.local</t>
+    <t>case2_valid4_1791567428307@company.local</t>
   </si>
   <si>
     <t>RECRUITER</t>
@@ -77,7 +77,7 @@
     <t/>
   </si>
   <si>
-    <t>case2_empty_name_1791476314118@company.local</t>
+    <t>case2_empty_name_1791567428307@company.local</t>
   </si>
   <si>
     <t>Tài chính</t>
@@ -86,13 +86,13 @@
     <t>Nhân sự Đúng 5</t>
   </si>
   <si>
-    <t>case2_valid5_1791476314118@company.local</t>
+    <t>case2_valid5_1791567428307@company.local</t>
   </si>
   <si>
     <t>Nhân sự Đúng 6</t>
   </si>
   <si>
-    <t>case2_valid6_1791476314118@company.local</t>
+    <t>case2_valid6_1791567428307@company.local</t>
   </si>
   <si>
     <t>Vận hành</t>
@@ -101,7 +101,7 @@
     <t>Nhân sự Lỗi 3 Role Sai</t>
   </si>
   <si>
-    <t>case2_invalid_role_1791476314118@company.local</t>
+    <t>case2_invalid_role_1791567428307@company.local</t>
   </si>
   <si>
     <t>INVALID_ROLE_XYZ</t>
@@ -110,7 +110,7 @@
     <t>Nhân sự Đúng 7</t>
   </si>
   <si>
-    <t>case2_valid7_1791476314118@company.local</t>
+    <t>case2_valid7_1791567428307@company.local</t>
   </si>
 </sst>
 </file>

--- a/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
+++ b/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Đúng 1</t>
   </si>
   <si>
-    <t>case2_valid1_1791567428307@company.local</t>
+    <t>case2_valid1_1791567643572@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
@@ -41,7 +41,7 @@
     <t>Nhân sự Đúng 2</t>
   </si>
   <si>
-    <t>case2_valid2_1791567428307@company.local</t>
+    <t>case2_valid2_1791567643572@company.local</t>
   </si>
   <si>
     <t>INTERVIEWER</t>
@@ -56,7 +56,7 @@
     <t>Nhân sự Đúng 3</t>
   </si>
   <si>
-    <t>case2_valid3_1791567428307@company.local</t>
+    <t>case2_valid3_1791567643572@company.local</t>
   </si>
   <si>
     <t>Nhân sự</t>
@@ -68,7 +68,7 @@
     <t>Nhân sự Đúng 4</t>
   </si>
   <si>
-    <t>case2_valid4_1791567428307@company.local</t>
+    <t>case2_valid4_1791567643572@company.local</t>
   </si>
   <si>
     <t>RECRUITER</t>
@@ -77,7 +77,7 @@
     <t/>
   </si>
   <si>
-    <t>case2_empty_name_1791567428307@company.local</t>
+    <t>case2_empty_name_1791567643572@company.local</t>
   </si>
   <si>
     <t>Tài chính</t>
@@ -86,13 +86,13 @@
     <t>Nhân sự Đúng 5</t>
   </si>
   <si>
-    <t>case2_valid5_1791567428307@company.local</t>
+    <t>case2_valid5_1791567643572@company.local</t>
   </si>
   <si>
     <t>Nhân sự Đúng 6</t>
   </si>
   <si>
-    <t>case2_valid6_1791567428307@company.local</t>
+    <t>case2_valid6_1791567643572@company.local</t>
   </si>
   <si>
     <t>Vận hành</t>
@@ -101,7 +101,7 @@
     <t>Nhân sự Lỗi 3 Role Sai</t>
   </si>
   <si>
-    <t>case2_invalid_role_1791567428307@company.local</t>
+    <t>case2_invalid_role_1791567643572@company.local</t>
   </si>
   <si>
     <t>INVALID_ROLE_XYZ</t>
@@ -110,7 +110,7 @@
     <t>Nhân sự Đúng 7</t>
   </si>
   <si>
-    <t>case2_valid7_1791567428307@company.local</t>
+    <t>case2_valid7_1791567643572@company.local</t>
   </si>
 </sst>
 </file>

--- a/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
+++ b/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Đúng 1</t>
   </si>
   <si>
-    <t>case2_valid1_1791567643572@company.local</t>
+    <t>case2_valid1_1791909724777@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
@@ -41,7 +41,7 @@
     <t>Nhân sự Đúng 2</t>
   </si>
   <si>
-    <t>case2_valid2_1791567643572@company.local</t>
+    <t>case2_valid2_1791909724777@company.local</t>
   </si>
   <si>
     <t>INTERVIEWER</t>
@@ -56,7 +56,7 @@
     <t>Nhân sự Đúng 3</t>
   </si>
   <si>
-    <t>case2_valid3_1791567643572@company.local</t>
+    <t>case2_valid3_1791909724777@company.local</t>
   </si>
   <si>
     <t>Nhân sự</t>
@@ -68,7 +68,7 @@
     <t>Nhân sự Đúng 4</t>
   </si>
   <si>
-    <t>case2_valid4_1791567643572@company.local</t>
+    <t>case2_valid4_1791909724777@company.local</t>
   </si>
   <si>
     <t>RECRUITER</t>
@@ -77,7 +77,7 @@
     <t/>
   </si>
   <si>
-    <t>case2_empty_name_1791567643572@company.local</t>
+    <t>case2_empty_name_1791909724777@company.local</t>
   </si>
   <si>
     <t>Tài chính</t>
@@ -86,13 +86,13 @@
     <t>Nhân sự Đúng 5</t>
   </si>
   <si>
-    <t>case2_valid5_1791567643572@company.local</t>
+    <t>case2_valid5_1791909724777@company.local</t>
   </si>
   <si>
     <t>Nhân sự Đúng 6</t>
   </si>
   <si>
-    <t>case2_valid6_1791567643572@company.local</t>
+    <t>case2_valid6_1791909724777@company.local</t>
   </si>
   <si>
     <t>Vận hành</t>
@@ -101,7 +101,7 @@
     <t>Nhân sự Lỗi 3 Role Sai</t>
   </si>
   <si>
-    <t>case2_invalid_role_1791567643572@company.local</t>
+    <t>case2_invalid_role_1791909724777@company.local</t>
   </si>
   <si>
     <t>INVALID_ROLE_XYZ</t>
@@ -110,7 +110,7 @@
     <t>Nhân sự Đúng 7</t>
   </si>
   <si>
-    <t>case2_valid7_1791567643572@company.local</t>
+    <t>case2_valid7_1791909724777@company.local</t>
   </si>
 </sst>
 </file>

--- a/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
+++ b/frontend/test-fixtures/case2_partial_7valid_3invalid.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Đúng 1</t>
   </si>
   <si>
-    <t>case2_valid1_1791567643572@company.local</t>
+    <t>case2_valid1_1792700857270@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
@@ -41,7 +41,7 @@
     <t>Nhân sự Đúng 2</t>
   </si>
   <si>
-    <t>case2_valid2_1791567643572@company.local</t>
+    <t>case2_valid2_1792700857270@company.local</t>
   </si>
   <si>
     <t>INTERVIEWER</t>
@@ -56,7 +56,7 @@
     <t>Nhân sự Đúng 3</t>
   </si>
   <si>
-    <t>case2_valid3_1791567643572@company.local</t>
+    <t>case2_valid3_1792700857270@company.local</t>
   </si>
   <si>
     <t>Nhân sự</t>
@@ -68,7 +68,7 @@
     <t>Nhân sự Đúng 4</t>
   </si>
   <si>
-    <t>case2_valid4_1791567643572@company.local</t>
+    <t>case2_valid4_1792700857270@company.local</t>
   </si>
   <si>
     <t>RECRUITER</t>
@@ -77,7 +77,7 @@
     <t/>
   </si>
   <si>
-    <t>case2_empty_name_1791567643572@company.local</t>
+    <t>case2_empty_name_1792700857270@company.local</t>
   </si>
   <si>
     <t>Tài chính</t>
@@ -86,13 +86,13 @@
     <t>Nhân sự Đúng 5</t>
   </si>
   <si>
-    <t>case2_valid5_1791567643572@company.local</t>
+    <t>case2_valid5_1792700857270@company.local</t>
   </si>
   <si>
     <t>Nhân sự Đúng 6</t>
   </si>
   <si>
-    <t>case2_valid6_1791567643572@company.local</t>
+    <t>case2_valid6_1792700857270@company.local</t>
   </si>
   <si>
     <t>Vận hành</t>
@@ -101,7 +101,7 @@
     <t>Nhân sự Lỗi 3 Role Sai</t>
   </si>
   <si>
-    <t>case2_invalid_role_1791567643572@company.local</t>
+    <t>case2_invalid_role_1792700857270@company.local</t>
   </si>
   <si>
     <t>INVALID_ROLE_XYZ</t>
@@ -110,7 +110,7 @@
     <t>Nhân sự Đúng 7</t>
   </si>
   <si>
-    <t>case2_valid7_1791567643572@company.local</t>
+    <t>case2_valid7_1792700857270@company.local</t>
   </si>
 </sst>
 </file>
